--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/ARKANSAS_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/ARKANSAS_2023.xlsx
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C170">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C260">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C269">
